--- a/nr-add-lipids/ig/observations-summary.xlsx
+++ b/nr-add-lipids/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="81">
   <si>
     <t>Profile</t>
   </si>
@@ -152,6 +152,21 @@
     <t>null#9279-1</t>
   </si>
   <si>
+    <t>mesures-observation-cholesterol-aspect</t>
+  </si>
+  <si>
+    <t>Aspect du cholestérol</t>
+  </si>
+  <si>
+    <t>LOINC#11158-3</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
     <t>mesures-observation-cholesterol-hdl</t>
   </si>
   <si>
@@ -161,12 +176,6 @@
     <t>LOINC#2085-9</t>
   </si>
   <si>
-    <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>mesures-observation-cholesterol-ldl</t>
   </si>
   <si>
@@ -174,6 +183,15 @@
   </si>
   <si>
     <t>LOINC#2089-1</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-ratio</t>
+  </si>
+  <si>
+    <t>Cholestérol Ratio</t>
+  </si>
+  <si>
+    <t>LOINC#11054-4</t>
   </si>
   <si>
     <t>mesures-observation-cholesterol-total</t>
@@ -370,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -941,22 +959,22 @@
         <v>61</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>19</v>
@@ -976,7 +994,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
@@ -985,13 +1003,13 @@
         <v>65</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
@@ -1017,10 +1035,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="F19" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>32</v>
@@ -1093,18 +1111,88 @@
         <v>16</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G22" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K21" t="s" s="2">
+      <c r="H22" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K23" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/nr-add-lipids/ig/observations-summary.xlsx
+++ b/nr-add-lipids/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="82">
   <si>
     <t>Profile</t>
   </si>
@@ -155,7 +155,7 @@
     <t>mesures-observation-cholesterol-aspect</t>
   </si>
   <si>
-    <t>Aspect du cholestérol</t>
+    <t>Cholestérol - aspect</t>
   </si>
   <si>
     <t>LOINC#11158-3</t>
@@ -164,22 +164,25 @@
     <t>dateTime, Period, Timing, instant</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>mesures-observation-cholesterol-hdl</t>
+  </si>
+  <si>
+    <t>Cholestérol - HDL</t>
+  </si>
+  <si>
+    <t>LOINC#2085-9</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>mesures-observation-cholesterol-hdl</t>
-  </si>
-  <si>
-    <t>Cholestérol HDL</t>
-  </si>
-  <si>
-    <t>LOINC#2085-9</t>
-  </si>
-  <si>
     <t>mesures-observation-cholesterol-ldl</t>
   </si>
   <si>
-    <t>Cholestérol LDL</t>
+    <t>Cholestérol - LDL</t>
   </si>
   <si>
     <t>LOINC#2089-1</t>
@@ -188,7 +191,7 @@
     <t>mesures-observation-cholesterol-ratio</t>
   </si>
   <si>
-    <t>Cholestérol Ratio</t>
+    <t>Cholestérol - Ratio LDL/HDL</t>
   </si>
   <si>
     <t>LOINC#11054-4</t>
@@ -197,7 +200,7 @@
     <t>mesures-observation-cholesterol-total</t>
   </si>
   <si>
-    <t>Cholestérol total</t>
+    <t>Cholestérol - total</t>
   </si>
   <si>
     <t>LOINC#2093-3</t>
@@ -206,7 +209,7 @@
     <t>mesures-observation-cholesterol-trigly</t>
   </si>
   <si>
-    <t>Cholestérol triglycerides</t>
+    <t>Cholestérol - triglycerides</t>
   </si>
   <si>
     <t>LOINC#2571-8</t>
@@ -869,7 +872,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>19</v>
@@ -883,10 +886,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>14</v>
@@ -895,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>14</v>
@@ -904,7 +907,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>19</v>
@@ -918,10 +921,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -930,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>14</v>
@@ -939,7 +942,7 @@
         <v>49</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>19</v>
@@ -953,10 +956,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -965,7 +968,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>14</v>
@@ -974,7 +977,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>19</v>
@@ -988,10 +991,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>14</v>
@@ -1000,7 +1003,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>14</v>
@@ -1009,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
@@ -1023,10 +1026,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>13</v>
@@ -1038,7 +1041,7 @@
         <v>14</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>32</v>
@@ -1058,10 +1061,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>13</v>
@@ -1070,7 +1073,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>16</v>
@@ -1093,10 +1096,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1105,7 +1108,7 @@
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>16</v>
@@ -1128,10 +1131,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1140,7 +1143,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>16</v>
@@ -1163,10 +1166,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1175,7 +1178,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>16</v>

--- a/nr-add-lipids/ig/observations-summary.xlsx
+++ b/nr-add-lipids/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
   <si>
     <t>Profile</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>null#8287-5</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
   </si>
   <si>
     <t>mesures-observation-pain-severity</t>
@@ -1076,7 +1079,7 @@
         <v>72</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>17</v>
@@ -1096,10 +1099,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>13</v>
@@ -1108,10 +1111,10 @@
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>32</v>
@@ -1131,10 +1134,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>13</v>
@@ -1143,10 +1146,10 @@
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>17</v>
@@ -1166,10 +1169,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>13</v>
@@ -1178,10 +1181,10 @@
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>17</v>

--- a/nr-add-lipids/ig/observations-summary.xlsx
+++ b/nr-add-lipids/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="86">
   <si>
     <t>Profile</t>
   </si>
@@ -224,16 +224,25 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS (extensible)</t>
   </si>
   <si>
+    <t>mesures-observation-hb1ac</t>
+  </si>
+  <si>
+    <t>Hémoglobine glyquée (Hb1Ac)</t>
+  </si>
+  <si>
+    <t>null#4548-4</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
+  </si>
+  <si>
     <t>mesures-observation-head-circumference</t>
   </si>
   <si>
     <t>Périmètre Crânien</t>
   </si>
   <si>
-    <t>null#8287-5</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
+    <t>null#9843-4, null#8287-5</t>
   </si>
   <si>
     <t>mesures-observation-pain-severity</t>
@@ -394,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1082,7 +1091,7 @@
         <v>73</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -1117,7 +1126,7 @@
         <v>73</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -1152,7 +1161,7 @@
         <v>73</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -1199,6 +1208,41 @@
         <v>14</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/nr-add-lipids/ig/observations-summary.xlsx
+++ b/nr-add-lipids/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="83">
   <si>
     <t>Profile</t>
   </si>
@@ -186,15 +186,6 @@
   </si>
   <si>
     <t>LOINC#2089-1</t>
-  </si>
-  <si>
-    <t>mesures-observation-cholesterol-ratio</t>
-  </si>
-  <si>
-    <t>Cholestérol - Ratio LDL/HDL</t>
-  </si>
-  <si>
-    <t>LOINC#11054-4</t>
   </si>
   <si>
     <t>mesures-observation-cholesterol-total</t>
@@ -403,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1009,22 +1000,22 @@
         <v>65</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="F18" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="G18" t="s" s="2">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>19</v>
@@ -1050,10 +1041,10 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>32</v>
@@ -1073,25 +1064,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="G20" t="s" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -1123,10 +1114,10 @@
         <v>76</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>18</v>
@@ -1158,10 +1149,10 @@
         <v>79</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
@@ -1193,7 +1184,7 @@
         <v>82</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>17</v>
@@ -1208,41 +1199,6 @@
         <v>14</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K24" t="s" s="2">
         <v>14</v>
       </c>
     </row>
